--- a/1adults-1days-chart.xlsx
+++ b/1adults-1days-chart.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="2" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="Цены" sheetId="1" r:id="rId4"/>
-    <sheet name="Загрузка" sheetId="2" r:id="rId5"/>
+    <sheet name="Ограниченная_загрузка" sheetId="2" r:id="rId5"/>
+    <sheet name="Загрузка" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
   <si>
     <t>Отели</t>
   </si>
@@ -67,9 +68,6 @@
   </si>
   <si>
     <t>Выборка</t>
-  </si>
-  <si>
-    <t>23.09.2021</t>
   </si>
   <si>
     <t>24.09.2021</t>
@@ -180,7 +178,7 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>Цены!$A$2:$A$4</c:f>
+              <c:f>Цены!$A$2:$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
               </c:strCache>
@@ -188,9 +186,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$B$2:$B$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$B$2:$B$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -211,9 +209,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$C$2:$C$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$C$2:$C$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -234,9 +232,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$D$2:$D$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$D$2:$D$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -257,9 +255,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$E$2:$E$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$E$2:$E$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -280,9 +278,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$F$2:$F$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$F$2:$F$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -303,9 +301,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$G$2:$G$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$G$2:$G$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -326,9 +324,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$H$2:$H$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$H$2:$H$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -349,9 +347,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$I$2:$I$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$I$2:$I$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -372,9 +370,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$J$2:$J$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$J$2:$J$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -395,9 +393,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$K$2:$K$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$K$2:$K$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -418,9 +416,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$L$2:$L$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$L$2:$L$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -441,9 +439,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$M$2:$M$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$M$2:$M$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -464,9 +462,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$N$2:$N$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$N$2:$N$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -487,9 +485,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$O$2:$O$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$O$2:$O$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -510,9 +508,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$P$2:$P$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$P$2:$P$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -533,9 +531,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$Q$2:$Q$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Цены!$Q$2:$Q$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -649,6 +647,243 @@
               <a:rPr b="0" i="0" u="none" strike="noStrike">
                 <a:latin typeface="Calibri"/>
               </a:rPr>
+              <a:t>Ограниченная_загрузка</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Ограниченная_загрузка!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Ограниченная_загрузка!$A$2:$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Ограниченная_загрузка!$B$2:$B$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Ограниченная_загрузка!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Ограниченная_загрузка!$C$2:$C$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Ограниченная_загрузка!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Ограниченная_загрузка!$D$2:$D$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Ограниченная_загрузка!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Ограниченная_загрузка!$E$2:$E$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Ограниченная_загрузка!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Ограниченная_загрузка!$F$2:$F$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="75091328"/>
+        <c:axId val="75089408"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="75091328"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="75089408"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="75089408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:prstDash val="solid"/>
+            <a:bevel/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:crossAx val="75089408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins footer="0.3" header="0.3" r="0.7" l="0.7" t="0.75" b="0.75"/>
+    <c:pageSetup orientation="portrait"/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr b="0" i="0" u="none" strike="noStrike">
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
               <a:t>Загрузка</a:t>
             </a:r>
           </a:p>
@@ -678,7 +913,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Загрузка!$A$2:$A$4</c:f>
+              <c:f>Загрузка!$A$2:$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
               </c:strCache>
@@ -686,9 +921,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$B$2:$B$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Загрузка!$B$2:$B$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -707,9 +942,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$C$2:$C$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Загрузка!$C$2:$C$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -728,9 +963,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$D$2:$D$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Загрузка!$D$2:$D$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -749,9 +984,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$E$2:$E$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Загрузка!$E$2:$E$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -770,9 +1005,240 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$F$2:$F$4</c:f>
-              <c:numCache>
-                <c:ptCount val="30"/>
+              <c:f>Загрузка!$F$2:$F$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$G$2:$G$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$H$2:$H$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$I$2:$I$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$J$2:$J$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$K$2:$K$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$L$2:$L$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$M$2:$M$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$N$2:$N$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$O$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$O$2:$O$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$P$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$P$2:$P$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Загрузка!$Q$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Загрузка!$Q$2:$Q$3</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -866,13 +1332,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
+      <xdr:col>67</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -903,13 +1369,50 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr name="Chart 1" id="1025"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>67</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -1226,7 +1729,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1287,52 +1790,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <v>44</v>
       </c>
       <c r="D2">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>122</v>
       </c>
       <c r="F2">
+        <v>126</v>
+      </c>
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>63</v>
-      </c>
       <c r="H2">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M2">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>39</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="P2">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="Q2">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -1340,25 +1843,25 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C3">
         <v>44</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E3">
         <v>122</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1373,72 +1876,19 @@
         <v>94</v>
       </c>
       <c r="M3">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>39</v>
       </c>
       <c r="O3">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="Q3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>35</v>
-      </c>
-      <c r="C4">
-        <v>44</v>
-      </c>
-      <c r="D4">
         <v>0</v>
-      </c>
-      <c r="E4">
-        <v>122</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>81</v>
-      </c>
-      <c r="H4">
-        <v>56</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>94</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>39</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>62</v>
-      </c>
-      <c r="Q4">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1463,7 +1913,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1477,7 +1927,7 @@
         <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
         <v>16</v>
@@ -1488,16 +1938,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C2">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="D2">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1505,33 +1955,200 @@
         <v>18</v>
       </c>
       <c r="B3">
+        <v>46</v>
+      </c>
+      <c r="C3">
+        <v>78</v>
+      </c>
+      <c r="D3">
+        <v>80</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
         <v>85</v>
       </c>
+      <c r="C2">
+        <v>71</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>88</v>
+      </c>
+      <c r="F2">
+        <v>92</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2">
+        <v>75</v>
+      </c>
+      <c r="M2">
+        <v>100</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>92</v>
+      </c>
+      <c r="P2">
+        <v>81</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>46</v>
+      </c>
       <c r="C3">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D3">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>46</v>
-      </c>
-      <c r="C4">
-        <v>79</v>
-      </c>
-      <c r="D4">
-        <v>82</v>
-      </c>
-      <c r="E4">
-        <v>46</v>
+        <v>88</v>
+      </c>
+      <c r="F3">
+        <v>92</v>
+      </c>
+      <c r="G3">
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>50</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>100</v>
+      </c>
+      <c r="L3">
+        <v>25</v>
+      </c>
+      <c r="M3">
+        <v>100</v>
+      </c>
+      <c r="N3">
+        <v>8</v>
+      </c>
+      <c r="O3">
+        <v>100</v>
+      </c>
+      <c r="P3">
+        <v>78</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/1adults-1days-chart.xlsx
+++ b/1adults-1days-chart.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="22">
   <si>
     <t>Отели</t>
   </si>
@@ -70,10 +70,16 @@
     <t>Выборка</t>
   </si>
   <si>
-    <t>24.09.2021</t>
+    <t>19.10.2021</t>
   </si>
   <si>
-    <t>25.09.2021</t>
+    <t>20.10.2021</t>
+  </si>
+  <si>
+    <t>21.10.2021</t>
+  </si>
+  <si>
+    <t>22.10.2021</t>
   </si>
   <si>
     <t>Рынок без KK и Лейкари</t>
@@ -178,7 +184,7 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>Цены!$A$2:$A$3</c:f>
+              <c:f>Цены!$A$2:$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
               </c:strCache>
@@ -186,9 +192,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -209,9 +215,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$C$2:$C$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -232,9 +238,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$D$2:$D$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$D$2:$D$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -255,9 +261,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$E$2:$E$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$E$2:$E$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -278,9 +284,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$F$2:$F$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$F$2:$F$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -301,9 +307,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$G$2:$G$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$G$2:$G$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -324,9 +330,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$H$2:$H$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$H$2:$H$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -347,9 +353,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$I$2:$I$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$I$2:$I$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -370,9 +376,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$J$2:$J$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$J$2:$J$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -393,9 +399,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$K$2:$K$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$K$2:$K$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -416,9 +422,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$L$2:$L$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$L$2:$L$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -439,9 +445,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$M$2:$M$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$M$2:$M$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -462,9 +468,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$N$2:$N$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$N$2:$N$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -485,9 +491,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$O$2:$O$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$O$2:$O$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -508,9 +514,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$P$2:$P$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$P$2:$P$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -531,9 +537,9 @@
           </c:spPr>
           <c:val>
             <c:numRef>
-              <c:f>Цены!$Q$2:$Q$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Цены!$Q$2:$Q$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -676,7 +682,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Ограниченная_загрузка!$A$2:$A$3</c:f>
+              <c:f>Ограниченная_загрузка!$A$2:$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
               </c:strCache>
@@ -684,9 +690,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Ограниченная_загрузка!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Ограниченная_загрузка!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -705,9 +711,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Ограниченная_загрузка!$C$2:$C$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Ограниченная_загрузка!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -726,9 +732,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Ограниченная_загрузка!$D$2:$D$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Ограниченная_загрузка!$D$2:$D$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -747,9 +753,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Ограниченная_загрузка!$E$2:$E$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Ограниченная_загрузка!$E$2:$E$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -768,9 +774,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Ограниченная_загрузка!$F$2:$F$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Ограниченная_загрузка!$F$2:$F$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -913,7 +919,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Загрузка!$A$2:$A$3</c:f>
+              <c:f>Загрузка!$A$2:$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
               </c:strCache>
@@ -921,9 +927,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -942,9 +948,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$C$2:$C$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -963,9 +969,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$D$2:$D$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$D$2:$D$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -984,9 +990,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$E$2:$E$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$E$2:$E$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1005,9 +1011,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$F$2:$F$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$F$2:$F$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1026,9 +1032,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$G$2:$G$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$G$2:$G$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1047,9 +1053,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$H$2:$H$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$H$2:$H$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1068,9 +1074,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$I$2:$I$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$I$2:$I$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1089,9 +1095,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$J$2:$J$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$J$2:$J$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1110,9 +1116,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$K$2:$K$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$K$2:$K$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1131,9 +1137,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$L$2:$L$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$L$2:$L$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1152,9 +1158,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$M$2:$M$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$M$2:$M$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1173,9 +1179,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$N$2:$N$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$N$2:$N$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1194,9 +1200,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$O$2:$O$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$O$2:$O$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1215,9 +1221,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$P$2:$P$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$P$2:$P$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1236,9 +1242,9 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>Загрузка!$Q$2:$Q$3</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
+              <c:f>Загрузка!$Q$2:$Q$5</c:f>
+              <c:numCache>
+                <c:ptCount val="4"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1729,7 +1735,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1790,22 +1796,22 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>44</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1820,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -1829,10 +1835,10 @@
         <v>39</v>
       </c>
       <c r="O2">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1843,7 +1849,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>44</v>
@@ -1852,28 +1858,28 @@
         <v>59</v>
       </c>
       <c r="E3">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F3">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L3">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -1885,9 +1891,115 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="Q3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>44</v>
+      </c>
+      <c r="D4">
+        <v>59</v>
+      </c>
+      <c r="E4">
+        <v>110</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>64</v>
+      </c>
+      <c r="H4">
+        <v>65</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>62</v>
+      </c>
+      <c r="K4">
+        <v>98</v>
+      </c>
+      <c r="L4">
+        <v>87</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>39</v>
+      </c>
+      <c r="O4">
+        <v>57</v>
+      </c>
+      <c r="P4">
+        <v>64</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>44</v>
+      </c>
+      <c r="D5">
+        <v>59</v>
+      </c>
+      <c r="E5">
+        <v>110</v>
+      </c>
+      <c r="F5">
+        <v>77</v>
+      </c>
+      <c r="G5">
+        <v>64</v>
+      </c>
+      <c r="H5">
+        <v>65</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>59</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>94</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>39</v>
+      </c>
+      <c r="O5">
+        <v>67</v>
+      </c>
+      <c r="P5">
+        <v>70</v>
+      </c>
+      <c r="Q5">
         <v>0</v>
       </c>
     </row>
@@ -1913,7 +2025,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1927,7 +2039,7 @@
         <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
         <v>16</v>
@@ -1938,10 +2050,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D2">
         <v>85</v>
@@ -1955,15 +2067,49 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D3">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>64</v>
+      </c>
+      <c r="D4">
+        <v>69</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>63</v>
+      </c>
+      <c r="D5">
+        <v>61</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
     </row>
@@ -1989,7 +2135,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -2050,22 +2196,22 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E2">
         <v>88</v>
       </c>
       <c r="F2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -2080,19 +2226,19 @@
         <v>100</v>
       </c>
       <c r="L2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M2">
         <v>100</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="P2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -2103,19 +2249,19 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E3">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>75</v>
@@ -2127,13 +2273,13 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="M3">
         <v>100</v>
@@ -2145,9 +2291,115 @@
         <v>100</v>
       </c>
       <c r="P3">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="Q3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <v>90</v>
+      </c>
+      <c r="E4">
+        <v>75</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>25</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>33</v>
+      </c>
+      <c r="K4">
+        <v>60</v>
+      </c>
+      <c r="L4">
+        <v>75</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>8</v>
+      </c>
+      <c r="O4">
+        <v>58</v>
+      </c>
+      <c r="P4">
+        <v>64</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>75</v>
+      </c>
+      <c r="F5">
+        <v>77</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>33</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>50</v>
+      </c>
+      <c r="P5">
+        <v>63</v>
+      </c>
+      <c r="Q5">
         <v>0</v>
       </c>
     </row>
